--- a/alumnos/Jose Gimenez/Casos de Prueba/Casos de Prueba Positivo y Negativo.xlsx
+++ b/alumnos/Jose Gimenez/Casos de Prueba/Casos de Prueba Positivo y Negativo.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
   <si>
     <t xml:space="preserve">Test case </t>
   </si>
@@ -37,10 +37,13 @@
     <t>Revisado por</t>
   </si>
   <si>
+    <t>Sebastian</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2.1</t>
+    <t>Navegador Chrome</t>
   </si>
   <si>
     <t>QA Tester’s Log</t>
@@ -148,6 +151,12 @@
     <t>Test the Login Negativo</t>
   </si>
   <si>
+    <t>Userid = cualquiera</t>
+  </si>
+  <si>
+    <t>Pass = cualquiera</t>
+  </si>
+  <si>
     <t>Verifique que al ingresar un ID de usuario y contraseña válidos, el cliente no pueda iniciar sesión</t>
   </si>
   <si>
@@ -169,7 +178,19 @@
     </r>
   </si>
   <si>
-    <t>As Expected</t>
+    <t>Dirigirse a la seccion SIGN-ON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirecciona a la seccion </t>
+  </si>
+  <si>
+    <t>Ingresar Usuario y contraseña no registrados</t>
+  </si>
+  <si>
+    <t>Login NO REGISTRADO</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
 </sst>
 </file>
@@ -210,8 +231,7 @@
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -219,6 +239,11 @@
       <sz val="8.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -238,12 +263,8 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -252,14 +273,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA4C2F4"/>
-        <bgColor rgb="FFA4C2F4"/>
+        <fgColor rgb="FF6D9EEB"/>
+        <bgColor rgb="FF6D9EEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4C2F4"/>
+        <bgColor rgb="FFA4C2F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -370,6 +397,9 @@
       </bottom>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -378,9 +408,6 @@
       </bottom>
     </border>
     <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -410,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -441,12 +468,14 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
@@ -454,7 +483,7 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -463,47 +492,45 @@
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="12" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -515,7 +542,7 @@
     </xf>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -524,18 +551,15 @@
     <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf borderId="13" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
@@ -549,10 +573,16 @@
     <xf borderId="18" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="18" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="top"/>
@@ -834,14 +864,16 @@
         <v>7</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="12"/>
+      <c r="F6" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="G6" s="11"/>
       <c r="H6" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6" s="11"/>
     </row>
@@ -860,14 +892,12 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+        <v>12</v>
+      </c>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -890,24 +920,26 @@
     </row>
     <row r="10">
       <c r="A10" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="21"/>
+      <c r="C10" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="D10" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <v>45243.0</v>
       </c>
       <c r="G10" s="11"/>
       <c r="H10" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -925,31 +957,31 @@
       <c r="K11" s="15"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="24" t="s">
+      <c r="A12" s="22" t="s">
         <v>17</v>
       </c>
+      <c r="B12" s="23" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="10"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>18</v>
+      <c r="D12" s="24"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>19</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
-      <c r="K12" s="25"/>
+      <c r="K12" s="24"/>
     </row>
     <row r="13">
-      <c r="A13" s="29">
+      <c r="A13" s="28">
         <v>1.0</v>
       </c>
-      <c r="B13" s="12"/>
+      <c r="B13" s="29"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
       <c r="E13" s="30"/>
@@ -957,7 +989,7 @@
         <v>1.0</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
@@ -965,10 +997,10 @@
       <c r="K13" s="11"/>
     </row>
     <row r="14">
-      <c r="A14" s="29">
+      <c r="A14" s="28">
         <v>2.0</v>
       </c>
-      <c r="B14" s="12"/>
+      <c r="B14" s="29"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
       <c r="E14" s="30"/>
@@ -976,7 +1008,7 @@
         <v>2.0</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
@@ -984,34 +1016,34 @@
       <c r="K14" s="11"/>
     </row>
     <row r="15">
-      <c r="A15" s="29">
+      <c r="A15" s="28">
         <v>3.0</v>
       </c>
-      <c r="B15" s="12"/>
+      <c r="B15" s="29"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
       <c r="E15" s="30"/>
       <c r="F15" s="31">
         <v>3.0</v>
       </c>
-      <c r="G15" s="12"/>
+      <c r="G15" s="29"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16">
-      <c r="A16" s="29">
+      <c r="A16" s="28">
         <v>4.0</v>
       </c>
-      <c r="B16" s="12"/>
+      <c r="B16" s="29"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11"/>
       <c r="E16" s="30"/>
       <c r="F16" s="31">
         <v>4.0</v>
       </c>
-      <c r="G16" s="12"/>
+      <c r="G16" s="29"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
@@ -1032,10 +1064,10 @@
     </row>
     <row r="18">
       <c r="A18" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
@@ -1062,22 +1094,22 @@
     </row>
     <row r="20">
       <c r="A20" s="34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C20" s="36"/>
       <c r="D20" s="37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="36"/>
       <c r="F20" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H20" s="36"/>
       <c r="I20" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" s="36"/>
     </row>
@@ -1095,130 +1127,130 @@
       <c r="K21" s="6"/>
     </row>
     <row r="22">
-      <c r="A22" s="29">
+      <c r="A22" s="28">
         <v>1.0</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="11"/>
       <c r="I22" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J22" s="10"/>
       <c r="K22" s="11"/>
     </row>
     <row r="23">
-      <c r="A23" s="29">
+      <c r="A23" s="28">
         <v>2.0</v>
       </c>
       <c r="B23" s="41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="11"/>
       <c r="I23" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="10"/>
       <c r="K23" s="11"/>
     </row>
     <row r="24">
-      <c r="A24" s="29">
+      <c r="A24" s="28">
         <v>3.0</v>
       </c>
       <c r="B24" s="43" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="44"/>
       <c r="D24" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="11"/>
       <c r="I24" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J24" s="10"/>
       <c r="K24" s="11"/>
     </row>
     <row r="25">
-      <c r="A25" s="29">
+      <c r="A25" s="28">
         <v>4.0</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="47"/>
-      <c r="E25" s="48"/>
+      <c r="E25" s="44"/>
       <c r="F25" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="11"/>
       <c r="I25" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J25" s="10"/>
       <c r="K25" s="11"/>
     </row>
     <row r="26">
-      <c r="A26" s="49">
+      <c r="A26" s="48">
         <v>5.0</v>
       </c>
-      <c r="B26" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="52" t="s">
+      <c r="B26" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="51"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="50"/>
       <c r="F26" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="11"/>
       <c r="I26" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="10"/>
       <c r="K26" s="11"/>
     </row>
     <row r="27">
-      <c r="A27" s="53"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="55"/>
-      <c r="K27" s="55"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="54"/>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
@@ -1249,19 +1281,19 @@
       <c r="K30" s="4"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="55" t="s">
         <v>1</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="56" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="57" t="s">
         <v>3</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
@@ -1270,25 +1302,27 @@
       <c r="K31" s="11"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="55" t="s">
         <v>5</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="57" t="s">
         <v>7</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="G32" s="11"/>
       <c r="H32" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K32" s="11"/>
     </row>
@@ -1307,11 +1341,11 @@
     </row>
     <row r="34">
       <c r="A34" s="17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
@@ -1337,24 +1371,26 @@
     </row>
     <row r="36">
       <c r="A36" s="20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B36" s="6"/>
-      <c r="C36" s="21"/>
+      <c r="C36" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="D36" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E36" s="6"/>
-      <c r="F36" s="22">
+      <c r="F36" s="21">
         <v>45243.0</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I36" s="6"/>
-      <c r="J36" s="9" t="s">
-        <v>15</v>
+      <c r="J36" s="41" t="s">
+        <v>16</v>
       </c>
       <c r="K36" s="11"/>
     </row>
@@ -1372,39 +1408,39 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="24" t="s">
+      <c r="A38" s="22" t="s">
         <v>17</v>
       </c>
+      <c r="B38" s="23" t="s">
+        <v>18</v>
+      </c>
       <c r="C38" s="10"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="28" t="s">
-        <v>18</v>
+      <c r="D38" s="24"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="27" t="s">
+        <v>19</v>
       </c>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
-      <c r="K38" s="25"/>
+      <c r="K38" s="24"/>
     </row>
     <row r="39">
-      <c r="A39" s="29">
+      <c r="A39" s="28">
         <v>1.0</v>
       </c>
-      <c r="B39" s="12"/>
+      <c r="B39" s="29"/>
       <c r="C39" s="10"/>
       <c r="D39" s="11"/>
       <c r="E39" s="30"/>
       <c r="F39" s="31">
         <v>1.0</v>
       </c>
-      <c r="G39" s="9" t="s">
-        <v>19</v>
+      <c r="G39" s="41" t="s">
+        <v>41</v>
       </c>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
@@ -1412,18 +1448,18 @@
       <c r="K39" s="11"/>
     </row>
     <row r="40">
-      <c r="A40" s="29">
+      <c r="A40" s="28">
         <v>2.0</v>
       </c>
-      <c r="B40" s="12"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="10"/>
       <c r="D40" s="11"/>
       <c r="E40" s="30"/>
       <c r="F40" s="31">
         <v>2.0</v>
       </c>
-      <c r="G40" s="9" t="s">
-        <v>20</v>
+      <c r="G40" s="41" t="s">
+        <v>42</v>
       </c>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
@@ -1431,34 +1467,34 @@
       <c r="K40" s="11"/>
     </row>
     <row r="41">
-      <c r="A41" s="29">
+      <c r="A41" s="28">
         <v>3.0</v>
       </c>
-      <c r="B41" s="12"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="10"/>
       <c r="D41" s="11"/>
       <c r="E41" s="30"/>
       <c r="F41" s="31">
         <v>3.0</v>
       </c>
-      <c r="G41" s="12"/>
+      <c r="G41" s="29"/>
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
       <c r="K41" s="11"/>
     </row>
     <row r="42">
-      <c r="A42" s="29">
+      <c r="A42" s="28">
         <v>4.0</v>
       </c>
-      <c r="B42" s="12"/>
+      <c r="B42" s="29"/>
       <c r="C42" s="10"/>
       <c r="D42" s="11"/>
       <c r="E42" s="30"/>
       <c r="F42" s="31">
         <v>4.0</v>
       </c>
-      <c r="G42" s="12"/>
+      <c r="G42" s="29"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
@@ -1479,10 +1515,10 @@
     </row>
     <row r="44">
       <c r="A44" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B44" s="57" t="s">
-        <v>40</v>
+        <v>22</v>
+      </c>
+      <c r="B44" s="58" t="s">
+        <v>43</v>
       </c>
       <c r="G44" s="16"/>
       <c r="H44" s="16"/>
@@ -1505,22 +1541,22 @@
     </row>
     <row r="46">
       <c r="A46" s="34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B46" s="35" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C46" s="36"/>
       <c r="D46" s="37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E46" s="36"/>
       <c r="F46" s="35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H46" s="36"/>
       <c r="I46" s="35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K46" s="36"/>
     </row>
@@ -1538,127 +1574,148 @@
       <c r="K47" s="6"/>
     </row>
     <row r="48">
-      <c r="A48" s="29">
+      <c r="A48" s="28">
         <v>1.0</v>
       </c>
       <c r="B48" s="40" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E48" s="11"/>
       <c r="F48" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G48" s="10"/>
       <c r="H48" s="11"/>
       <c r="I48" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J48" s="10"/>
       <c r="K48" s="11"/>
     </row>
     <row r="49">
-      <c r="A49" s="29">
+      <c r="A49" s="28">
         <v>2.0</v>
       </c>
-      <c r="B49" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="11"/>
+      <c r="B49" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="44"/>
       <c r="D49" s="42" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E49" s="11"/>
       <c r="F49" s="9" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G49" s="10"/>
       <c r="H49" s="11"/>
       <c r="I49" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J49" s="10"/>
       <c r="K49" s="11"/>
     </row>
     <row r="50">
-      <c r="A50" s="29">
+      <c r="A50" s="28">
         <v>3.0</v>
       </c>
-      <c r="B50" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" s="44"/>
-      <c r="D50" s="9" t="s">
-        <v>34</v>
+      <c r="B50" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="11"/>
+      <c r="D50" s="41" t="s">
+        <v>48</v>
       </c>
       <c r="E50" s="11"/>
       <c r="F50" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="11"/>
-      <c r="I50" s="9" t="s">
-        <v>15</v>
+      <c r="I50" s="41" t="s">
+        <v>49</v>
       </c>
       <c r="J50" s="10"/>
       <c r="K50" s="11"/>
     </row>
     <row r="51">
-      <c r="A51" s="29">
+      <c r="A51" s="28">
         <v>4.0</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="B51" s="9"/>
       <c r="C51" s="11"/>
-      <c r="D51" s="42" t="s">
-        <v>37</v>
-      </c>
+      <c r="D51" s="42"/>
       <c r="E51" s="11"/>
-      <c r="F51" s="9" t="s">
-        <v>30</v>
-      </c>
+      <c r="F51" s="9"/>
       <c r="G51" s="10"/>
       <c r="H51" s="11"/>
-      <c r="I51" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="I51" s="9"/>
       <c r="J51" s="10"/>
       <c r="K51" s="11"/>
     </row>
     <row r="52">
-      <c r="A52" s="29">
+      <c r="A52" s="28">
         <v>5.0</v>
       </c>
       <c r="B52" s="47"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="12"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="29"/>
       <c r="E52" s="11"/>
-      <c r="F52" s="12"/>
+      <c r="F52" s="29"/>
       <c r="G52" s="10"/>
       <c r="H52" s="11"/>
-      <c r="I52" s="12"/>
+      <c r="I52" s="29"/>
       <c r="J52" s="10"/>
       <c r="K52" s="11"/>
     </row>
     <row r="53">
-      <c r="A53" s="58"/>
-      <c r="B53" s="12"/>
+      <c r="A53" s="59"/>
+      <c r="B53" s="29"/>
       <c r="C53" s="11"/>
-      <c r="D53" s="12"/>
+      <c r="D53" s="29"/>
       <c r="E53" s="11"/>
-      <c r="F53" s="12"/>
+      <c r="F53" s="29"/>
       <c r="G53" s="10"/>
       <c r="H53" s="11"/>
-      <c r="I53" s="12"/>
+      <c r="I53" s="29"/>
       <c r="J53" s="10"/>
       <c r="K53" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="100">
+  <mergeCells count="106">
+    <mergeCell ref="D46:E47"/>
+    <mergeCell ref="F46:H47"/>
+    <mergeCell ref="I46:K47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="D25:E25"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:K5"/>
@@ -1673,6 +1730,7 @@
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C8:E8"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="G12:K12"/>
     <mergeCell ref="B13:D13"/>
@@ -1688,39 +1746,14 @@
     <mergeCell ref="D20:E21"/>
     <mergeCell ref="F20:H21"/>
     <mergeCell ref="I20:K21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:K23"/>
     <mergeCell ref="F27:H27"/>
     <mergeCell ref="I27:K27"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:K25"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="D46:E47"/>
-    <mergeCell ref="F46:H47"/>
-    <mergeCell ref="I46:K47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:K31"/>
     <mergeCell ref="D32:E32"/>
@@ -1751,6 +1784,8 @@
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="F51:H51"/>
     <mergeCell ref="F53:H53"/>
     <mergeCell ref="I53:K53"/>
@@ -1758,7 +1793,6 @@
     <mergeCell ref="F52:H52"/>
     <mergeCell ref="I52:K52"/>
     <mergeCell ref="D53:E53"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B22"/>
